--- a/data/LMIS_HIV_category.xlsx
+++ b/data/LMIS_HIV_category.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://psiorg-my.sharepoint.com/personal/bokola_psi_org/Documents/Documents/LMIS-data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bokola\ScrapeLMIS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{BE427364-D293-43D3-B667-7F83787B0930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7B1A6CD-9B75-45B0-8805-D806C69978CE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8EDC00-D337-44D1-BDCF-FB1673113485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{18D1138D-402F-4E8E-A8E3-7FB0CCBBCA8D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="40">
   <si>
     <t>Product</t>
   </si>
@@ -159,9 +159,6 @@
   </si>
   <si>
     <t>Pima Thermal Paper</t>
-  </si>
-  <si>
-    <t>HIV Monitorin</t>
   </si>
 </sst>
 </file>
@@ -793,7 +790,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
